--- a/artfynd/A 21722-2019 artfynd.xlsx
+++ b/artfynd/A 21722-2019 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126012853</v>
+        <v>126012801</v>
       </c>
       <c r="B2" t="n">
         <v>56843</v>
@@ -710,12 +710,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>536113</v>
+        <v>536078</v>
       </c>
       <c r="R2" t="n">
-        <v>6546531</v>
+        <v>6546523</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126012801</v>
+        <v>126012853</v>
       </c>
       <c r="B3" t="n">
         <v>56843</v>
@@ -821,12 +821,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536078</v>
+        <v>536113</v>
       </c>
       <c r="R3" t="n">
-        <v>6546523</v>
+        <v>6546531</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,12 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 21722-2019 artfynd.xlsx
+++ b/artfynd/A 21722-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126012801</v>
       </c>
       <c r="B2" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>126012853</v>
       </c>
       <c r="B3" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>126012800</v>
       </c>
       <c r="B4" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>126012854</v>
       </c>
       <c r="B5" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 21722-2019 artfynd.xlsx
+++ b/artfynd/A 21722-2019 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126012801</v>
+        <v>126012853</v>
       </c>
       <c r="B2" t="n">
         <v>56844</v>
@@ -710,12 +710,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>536078</v>
+        <v>536113</v>
       </c>
       <c r="R2" t="n">
-        <v>6546523</v>
+        <v>6546531</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126012853</v>
+        <v>126012801</v>
       </c>
       <c r="B3" t="n">
         <v>56844</v>
@@ -821,12 +821,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536113</v>
+        <v>536078</v>
       </c>
       <c r="R3" t="n">
-        <v>6546531</v>
+        <v>6546523</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,12 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 21722-2019 artfynd.xlsx
+++ b/artfynd/A 21722-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126012853</v>
       </c>
       <c r="B2" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>126012801</v>
       </c>
       <c r="B3" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>126012800</v>
       </c>
       <c r="B4" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>126012854</v>
       </c>
       <c r="B5" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 21722-2019 artfynd.xlsx
+++ b/artfynd/A 21722-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126012853</v>
       </c>
       <c r="B2" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>126012801</v>
       </c>
       <c r="B3" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>126012800</v>
       </c>
       <c r="B4" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>126012854</v>
       </c>
       <c r="B5" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
